--- a/测试文件/饲养标准模板.xlsx
+++ b/测试文件/饲养标准模板.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +58,17 @@
       <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -92,7 +103,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -106,11 +117,25 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -135,6 +160,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,673 +535,740 @@
   <dimension ref="A1:AE8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>标准名称</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>猪消化能MC/Kg</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>禽代谢能MC/Kg</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>综合净能(牛)MC/Kg</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>羊消化能MC/Kg</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>消化能(其他)MC/Kg</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>粗蛋白%</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>粗脂肪%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>粗纤维%</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>粗灰分%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>钙%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>总磷%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>非植酸磷%</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>食盐%</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>赖氨酸%</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>蛋氨酸%</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>蛋胱氨酸%</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>胱氨酸%</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>色氨酸%</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>苏氨酸%</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>异亮氨酸%</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>亮氨酸%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>缬氨酸%</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="9" t="inlineStr">
         <is>
           <t>苯丙氨酸%</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="9" t="inlineStr">
         <is>
           <t>干物质%</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="9" t="inlineStr">
         <is>
           <t>中性洗涤纤维%</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="9" t="inlineStr">
         <is>
           <t>酸性洗涤纤维%</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="9" t="inlineStr">
         <is>
           <t>钠%</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="9" t="inlineStr">
         <is>
           <t>钾%</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" s="9" t="inlineStr">
         <is>
           <t>氯%</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" s="9" t="inlineStr">
         <is>
           <t>亚油酸%</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>猪-生长育肥30~60kg</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="10" t="n">
         <v>2.95</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="10" t="n">
         <v>0.42</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="10" t="n">
         <v>0.16</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="10" t="n">
         <v>0.23</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="10" t="n">
         <v>0.64</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="P2" s="10" t="n">
         <v>0.27</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="Q2" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="R2" s="10" t="n">
         <v>0.34</v>
       </c>
-      <c r="S2" s="3" t="n">
+      <c r="S2" s="10" t="n">
         <v>0.16</v>
       </c>
-      <c r="T2" s="3" t="n">
+      <c r="T2" s="10" t="n">
         <v>0.42</v>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="W2" s="3" t="n">
+      <c r="W2" s="10" t="n">
         <v>0.66</v>
       </c>
-      <c r="X2" s="3" t="n">
+      <c r="X2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="Y2" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="AB2" s="3" t="n">
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AC2" s="10" t="n">
         <v>0.18</v>
       </c>
-      <c r="AD2" s="3" t="n">
+      <c r="AD2" s="10" t="n">
         <v>0.08</v>
       </c>
+      <c r="AE2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>禽-肉鸡0~3周龄</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="10" t="n">
         <v>0.16</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O3" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="P3" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="Q3" s="10" t="n">
         <v>0.73</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="R3" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="S3" s="3" t="n">
+      <c r="S3" s="10" t="n">
         <v>0.58</v>
       </c>
-      <c r="T3" s="3" t="n">
+      <c r="T3" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="W3" s="3" t="n">
+      <c r="W3" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="X3" s="3" t="n">
+      <c r="X3" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="Y3" s="3" t="n">
+      <c r="Y3" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="AB3" s="3" t="n">
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="AC3" s="3" t="n">
+      <c r="AC3" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="AD3" s="3" t="n">
+      <c r="AD3" s="10" t="n">
         <v>0.1</v>
       </c>
+      <c r="AE3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>禽-蛋鸡产蛋期</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n">
         <v>16.5</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="10" t="n">
         <v>0.32</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" s="10" t="n">
         <v>0.82</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="P4" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="10" t="n">
         <v>0.58</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="10" t="n">
         <v>0.17</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="T4" s="3" t="n">
+      <c r="T4" s="10" t="n">
         <v>0.55</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="Y4" s="3" t="n">
+      <c r="Y4" s="10" t="n">
         <v>0.55</v>
       </c>
-      <c r="AB4" s="3" t="n">
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="AC4" s="3" t="n">
+      <c r="AC4" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="AD4" s="3" t="n">
+      <c r="AD4" s="10" t="n">
         <v>0.08</v>
       </c>
+      <c r="AE4" s="10" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>牛-奶牛泌乳中期600kg</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n">
         <v>1.62</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n">
         <v>16.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="10" t="n">
         <v>0.26</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="10" t="n">
         <v>0.18</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="O5" s="10" t="n">
         <v>0.85</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="P5" s="10" t="n">
         <v>0.26</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="10" t="n">
         <v>0.38</v>
       </c>
-      <c r="T5" s="3" t="n">
+      <c r="T5" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="U5" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="10" t="n">
         <v>0.75</v>
       </c>
-      <c r="X5" s="3" t="n">
+      <c r="X5" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" s="10" t="n">
         <v>0.65</v>
       </c>
-      <c r="AB5" s="3" t="n">
+      <c r="Z5" s="10" t="n"/>
+      <c r="AA5" s="10" t="n"/>
+      <c r="AB5" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="AC5" s="3" t="n">
+      <c r="AC5" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="AD5" s="3" t="n">
+      <c r="AD5" s="10" t="n">
         <v>0.06</v>
       </c>
+      <c r="AE5" s="10" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>牛-肉牛育肥期300kg</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n">
         <v>1.78</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="10" t="n"/>
+      <c r="K6" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="10" t="n">
         <v>0.26</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="10" t="n">
         <v>0.18</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="10" t="n">
         <v>0.55</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="P6" s="10" t="n">
         <v>0.18</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="S6" s="3" t="n">
+      <c r="S6" s="10" t="n">
         <v>0.28</v>
       </c>
-      <c r="T6" s="3" t="n">
+      <c r="T6" s="10" t="n">
         <v>0.38</v>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="U6" s="10" t="n">
         <v>0.55</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="10" t="n">
         <v>0.58</v>
       </c>
-      <c r="X6" s="3" t="n">
+      <c r="X6" s="10" t="n">
         <v>0.65</v>
       </c>
-      <c r="Y6" s="3" t="n">
+      <c r="Y6" s="10" t="n">
         <v>0.48</v>
       </c>
-      <c r="AB6" s="3" t="n">
+      <c r="Z6" s="10" t="n"/>
+      <c r="AA6" s="10" t="n"/>
+      <c r="AB6" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="AC6" s="3" t="n">
+      <c r="AC6" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="AD6" s="3" t="n">
+      <c r="AD6" s="10" t="n">
         <v>0.05</v>
       </c>
+      <c r="AE6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>羊-育肥羔羊20kg</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="10" t="n">
         <v>0.14</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" s="10" t="n">
         <v>0.62</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="P7" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="10" t="n">
         <v>0.18</v>
       </c>
-      <c r="S7" s="3" t="n">
+      <c r="S7" s="10" t="n">
         <v>0.32</v>
       </c>
-      <c r="T7" s="3" t="n">
+      <c r="T7" s="10" t="n">
         <v>0.42</v>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="10" t="n">
         <v>0.65</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="10" t="n">
         <v>0.62</v>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="X7" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="Y7" s="3" t="n">
+      <c r="Y7" s="10" t="n">
         <v>0.52</v>
       </c>
-      <c r="AB7" s="3" t="n">
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="10" t="n"/>
+      <c r="AB7" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="AC7" s="3" t="n">
+      <c r="AC7" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="AD7" s="3" t="n">
+      <c r="AD7" s="10" t="n">
         <v>0.05</v>
       </c>
+      <c r="AE7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>其他-猫成年维持期</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O8" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="P8" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S8" s="10" t="n">
         <v>0.55</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="T8" s="10" t="n">
         <v>0.65</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X8" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y8" s="3" t="n">
+      <c r="Y8" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="AB8" s="3" t="n">
+      <c r="Z8" s="10" t="n"/>
+      <c r="AA8" s="10" t="n"/>
+      <c r="AB8" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AC8" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="AD8" s="3" t="n">
+      <c r="AD8" s="10" t="n">
         <v>0.12</v>
       </c>
+      <c r="AE8" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
